--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3523" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6C39446-81A7-44E7-A317-B8505509A673}"/>
+  <xr:revisionPtr revIDLastSave="3531" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C81B679-A5D7-4EB9-A606-5C491C85F135}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4848" uniqueCount="91">
   <si>
     <t>Sucursal</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Líder Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
   </si>
 </sst>
 </file>
@@ -32118,8 +32121,30 @@
       </c>
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1236" s="2"/>
-      <c r="G1236"/>
+      <c r="A1236" s="2">
+        <v>46207</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1236">
+        <v>1042774546</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1236">
+        <v>0</v>
+      </c>
+      <c r="H1236">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1237" s="2"/>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3531" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C81B679-A5D7-4EB9-A606-5C491C85F135}"/>
+  <xr:revisionPtr revIDLastSave="3534" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{078FDC88-495C-4B55-934F-BDB94B58D607}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4848" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4852" uniqueCount="92">
   <si>
     <t>Sucursal</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
   </si>
 </sst>
 </file>
@@ -32147,8 +32150,30 @@
       </c>
     </row>
     <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1237" s="2"/>
-      <c r="G1237"/>
+      <c r="A1237" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1237">
+        <v>1037548867</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1237">
+        <v>0</v>
+      </c>
+      <c r="H1237">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1238" s="2"/>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3607" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A55C430-A499-46B0-9FA1-4FEB7FF66633}"/>
+  <xr:revisionPtr revIDLastSave="3627" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE3246D8-98AA-4E2E-9F1E-2AC5851567E7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -2520,7 +2520,7 @@
         <v>46206</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C70">
         <v>1039597884</v>
@@ -2546,7 +2546,7 @@
         <v>46206</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C71">
         <v>1039597884</v>
@@ -3439,7 +3439,7 @@
         <v>74</v>
       </c>
       <c r="E105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F105" t="s">
         <v>59</v>
@@ -5233,7 +5233,7 @@
         <v>74</v>
       </c>
       <c r="E174" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F174" t="s">
         <v>60</v>
@@ -5571,7 +5571,7 @@
         <v>74</v>
       </c>
       <c r="E187" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F187" t="s">
         <v>60</v>
@@ -5831,7 +5831,7 @@
         <v>74</v>
       </c>
       <c r="E197" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F197" t="s">
         <v>60</v>
@@ -6004,7 +6004,7 @@
         <v>46206</v>
       </c>
       <c r="B204" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C204">
         <v>1039597884</v>
@@ -6117,7 +6117,7 @@
         <v>74</v>
       </c>
       <c r="E208" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F208" t="s">
         <v>60</v>
@@ -7330,7 +7330,7 @@
         <v>46206</v>
       </c>
       <c r="B255" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C255">
         <v>1039597884</v>
@@ -9280,7 +9280,7 @@
         <v>46204</v>
       </c>
       <c r="B330" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C330">
         <v>1233344333</v>
@@ -12530,7 +12530,7 @@
         <v>46205</v>
       </c>
       <c r="B455" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C455">
         <v>1017284920</v>
@@ -13102,7 +13102,7 @@
         <v>46205</v>
       </c>
       <c r="B477" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C477">
         <v>1017284920</v>
@@ -13700,7 +13700,7 @@
         <v>46206</v>
       </c>
       <c r="B500" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C500">
         <v>1039597884</v>
@@ -16231,7 +16231,7 @@
         <v>74</v>
       </c>
       <c r="E597" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F597" t="s">
         <v>59</v>
@@ -16543,7 +16543,7 @@
         <v>74</v>
       </c>
       <c r="E609" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F609" t="s">
         <v>60</v>
@@ -17626,7 +17626,7 @@
         <v>46206</v>
       </c>
       <c r="B651" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C651">
         <v>1039597884</v>
@@ -17765,7 +17765,7 @@
         <v>74</v>
       </c>
       <c r="E656" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F656" t="s">
         <v>57</v>
@@ -17921,7 +17921,7 @@
         <v>74</v>
       </c>
       <c r="E662" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F662" t="s">
         <v>57</v>
@@ -17947,7 +17947,7 @@
         <v>74</v>
       </c>
       <c r="E663" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F663" t="s">
         <v>60</v>
@@ -17973,7 +17973,7 @@
         <v>74</v>
       </c>
       <c r="E664" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F664" t="s">
         <v>60</v>
@@ -18025,7 +18025,7 @@
         <v>74</v>
       </c>
       <c r="E666" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F666" t="s">
         <v>60</v>
@@ -18077,7 +18077,7 @@
         <v>74</v>
       </c>
       <c r="E668" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F668" t="s">
         <v>60</v>
@@ -18103,7 +18103,7 @@
         <v>74</v>
       </c>
       <c r="E669" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F669" t="s">
         <v>60</v>
@@ -18129,7 +18129,7 @@
         <v>74</v>
       </c>
       <c r="E670" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F670" t="s">
         <v>60</v>
@@ -18233,7 +18233,7 @@
         <v>74</v>
       </c>
       <c r="E674" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F674" t="s">
         <v>60</v>
@@ -18337,7 +18337,7 @@
         <v>74</v>
       </c>
       <c r="E678" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F678" t="s">
         <v>60</v>
@@ -18363,7 +18363,7 @@
         <v>74</v>
       </c>
       <c r="E679" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F679" t="s">
         <v>59</v>
@@ -18389,7 +18389,7 @@
         <v>74</v>
       </c>
       <c r="E680" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F680" t="s">
         <v>57</v>
@@ -18441,7 +18441,7 @@
         <v>74</v>
       </c>
       <c r="E682" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F682" t="s">
         <v>59</v>
@@ -18545,7 +18545,7 @@
         <v>74</v>
       </c>
       <c r="E686" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F686" t="s">
         <v>60</v>
@@ -18571,7 +18571,7 @@
         <v>74</v>
       </c>
       <c r="E687" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F687" t="s">
         <v>60</v>
@@ -18701,7 +18701,7 @@
         <v>74</v>
       </c>
       <c r="E692" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F692" t="s">
         <v>60</v>
@@ -18727,7 +18727,7 @@
         <v>74</v>
       </c>
       <c r="E693" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F693" t="s">
         <v>60</v>
@@ -18753,7 +18753,7 @@
         <v>74</v>
       </c>
       <c r="E694" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F694" t="s">
         <v>59</v>
@@ -18831,7 +18831,7 @@
         <v>74</v>
       </c>
       <c r="E697" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F697" t="s">
         <v>59</v>
@@ -18857,7 +18857,7 @@
         <v>74</v>
       </c>
       <c r="E698" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F698" t="s">
         <v>60</v>
@@ -18883,7 +18883,7 @@
         <v>74</v>
       </c>
       <c r="E699" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F699" t="s">
         <v>60</v>
@@ -18909,7 +18909,7 @@
         <v>74</v>
       </c>
       <c r="E700" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F700" t="s">
         <v>60</v>
@@ -21769,7 +21769,7 @@
         <v>74</v>
       </c>
       <c r="E810" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F810" t="s">
         <v>60</v>
@@ -23589,7 +23589,7 @@
         <v>74</v>
       </c>
       <c r="E880" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F880" t="s">
         <v>60</v>
@@ -23615,7 +23615,7 @@
         <v>74</v>
       </c>
       <c r="E881" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F881" t="s">
         <v>57</v>
@@ -23788,7 +23788,7 @@
         <v>46207</v>
       </c>
       <c r="B888" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C888">
         <v>1039597884</v>
@@ -24057,7 +24057,7 @@
         <v>74</v>
       </c>
       <c r="E898" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F898" t="s">
         <v>57</v>
@@ -26059,7 +26059,7 @@
         <v>74</v>
       </c>
       <c r="E975" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F975" t="s">
         <v>59</v>
@@ -26085,7 +26085,7 @@
         <v>74</v>
       </c>
       <c r="E976" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F976" t="s">
         <v>59</v>
@@ -26111,7 +26111,7 @@
         <v>74</v>
       </c>
       <c r="E977" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F977" t="s">
         <v>60</v>
@@ -26674,7 +26674,7 @@
         <v>46207</v>
       </c>
       <c r="B999" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C999">
         <v>1039597884</v>
@@ -26726,7 +26726,7 @@
         <v>46206</v>
       </c>
       <c r="B1001" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1001">
         <v>1039597884</v>
@@ -26891,7 +26891,7 @@
         <v>74</v>
       </c>
       <c r="E1007" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1007" t="s">
         <v>60</v>
@@ -28286,7 +28286,7 @@
         <v>46204</v>
       </c>
       <c r="B1061" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C1061">
         <v>1000922411</v>
@@ -28451,7 +28451,7 @@
         <v>74</v>
       </c>
       <c r="E1067" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1067" t="s">
         <v>57</v>
@@ -28659,7 +28659,7 @@
         <v>74</v>
       </c>
       <c r="E1075" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1075" t="s">
         <v>60</v>
@@ -30652,7 +30652,7 @@
         <v>46205</v>
       </c>
       <c r="B1152" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C1152">
         <v>1017284920</v>
@@ -30678,7 +30678,7 @@
         <v>46205</v>
       </c>
       <c r="B1153" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C1153">
         <v>1017284920</v>
@@ -31909,7 +31909,7 @@
         <v>74</v>
       </c>
       <c r="E1200" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1200" t="s">
         <v>60</v>
@@ -32238,7 +32238,7 @@
         <v>46207</v>
       </c>
       <c r="B1213" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1213">
         <v>1039597884</v>
@@ -34743,7 +34743,7 @@
         <v>74</v>
       </c>
       <c r="E1309" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1309" t="s">
         <v>57</v>
@@ -36225,7 +36225,7 @@
         <v>74</v>
       </c>
       <c r="E1366" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1366" t="s">
         <v>59</v>
@@ -36979,7 +36979,7 @@
         <v>74</v>
       </c>
       <c r="E1395" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1395" t="s">
         <v>60</v>
@@ -37620,7 +37620,7 @@
         <v>46207</v>
       </c>
       <c r="B1420" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1420">
         <v>1039597884</v>
@@ -37828,7 +37828,7 @@
         <v>46205</v>
       </c>
       <c r="B1428" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C1428">
         <v>1017284920</v>
@@ -37941,7 +37941,7 @@
         <v>74</v>
       </c>
       <c r="E1432" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1432" t="s">
         <v>60</v>
@@ -39761,7 +39761,7 @@
         <v>74</v>
       </c>
       <c r="E1502" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1502" t="s">
         <v>60</v>
@@ -42621,7 +42621,7 @@
         <v>74</v>
       </c>
       <c r="E1612" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1612" t="s">
         <v>59</v>
@@ -43453,7 +43453,7 @@
         <v>74</v>
       </c>
       <c r="E1644" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1644" t="s">
         <v>60</v>
@@ -44961,7 +44961,7 @@
         <v>74</v>
       </c>
       <c r="E1702" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1702" t="s">
         <v>59</v>
@@ -45559,7 +45559,7 @@
         <v>74</v>
       </c>
       <c r="E1725" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1725" t="s">
         <v>60</v>
@@ -46928,7 +46928,7 @@
         <v>46207</v>
       </c>
       <c r="B1778" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1778">
         <v>1039597884</v>
@@ -48020,7 +48020,7 @@
         <v>46205</v>
       </c>
       <c r="B1820" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C1820">
         <v>1017284920</v>
@@ -48800,7 +48800,7 @@
         <v>46207</v>
       </c>
       <c r="B1850" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1850">
         <v>1039597884</v>
@@ -51773,7 +51773,7 @@
         <v>74</v>
       </c>
       <c r="E1964" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1964" t="s">
         <v>57</v>
@@ -52345,7 +52345,7 @@
         <v>74</v>
       </c>
       <c r="E1986" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1986" t="s">
         <v>59</v>
@@ -52839,7 +52839,7 @@
         <v>74</v>
       </c>
       <c r="E2005" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2005" t="s">
         <v>59</v>
@@ -52865,7 +52865,7 @@
         <v>74</v>
       </c>
       <c r="E2006" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2006" t="s">
         <v>59</v>
@@ -54295,7 +54295,7 @@
         <v>74</v>
       </c>
       <c r="E2061" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2061" t="s">
         <v>59</v>
@@ -54338,7 +54338,7 @@
         <v>46206</v>
       </c>
       <c r="B2063" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C2063">
         <v>1039597884</v>
@@ -56054,7 +56054,7 @@
         <v>46205</v>
       </c>
       <c r="B2129" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C2129">
         <v>1017284920</v>
@@ -56834,7 +56834,7 @@
         <v>46204</v>
       </c>
       <c r="B2159" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C2159">
         <v>1233344333</v>
@@ -57042,7 +57042,7 @@
         <v>46204</v>
       </c>
       <c r="B2167" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C2167">
         <v>1233344333</v>
@@ -57406,7 +57406,7 @@
         <v>46210</v>
       </c>
       <c r="B2181" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C2181">
         <v>1039597884</v>
